--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370850</v>
       </c>
       <c r="B2" t="n">
-        <v>78532</v>
+        <v>78537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137370859</v>
       </c>
       <c r="B29" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137370865</v>
       </c>
       <c r="B30" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137370854</v>
       </c>
       <c r="B31" t="n">
-        <v>83512</v>
+        <v>83517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>137370856</v>
       </c>
       <c r="B108" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>137370860</v>
       </c>
       <c r="B109" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>137370861</v>
       </c>
       <c r="B110" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>137370862</v>
       </c>
       <c r="B111" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>137370864</v>
       </c>
       <c r="B114" t="n">
-        <v>83505</v>
+        <v>83510</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>137370851</v>
       </c>
       <c r="B137" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>137370868</v>
       </c>
       <c r="B139" t="n">
-        <v>78521</v>
+        <v>78526</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370850</v>
       </c>
       <c r="B2" t="n">
-        <v>78537</v>
+        <v>78548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137370859</v>
       </c>
       <c r="B29" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137370865</v>
       </c>
       <c r="B30" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137370854</v>
       </c>
       <c r="B31" t="n">
-        <v>83517</v>
+        <v>83528</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>137370856</v>
       </c>
       <c r="B108" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>137370860</v>
       </c>
       <c r="B109" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>137370861</v>
       </c>
       <c r="B110" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>137370862</v>
       </c>
       <c r="B111" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>137370864</v>
       </c>
       <c r="B114" t="n">
-        <v>83510</v>
+        <v>83521</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>137370868</v>
       </c>
       <c r="B139" t="n">
-        <v>78526</v>
+        <v>78537</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370850</v>
       </c>
       <c r="B2" t="n">
-        <v>78548</v>
+        <v>78549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137370859</v>
       </c>
       <c r="B29" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137370865</v>
       </c>
       <c r="B30" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137370854</v>
       </c>
       <c r="B31" t="n">
-        <v>83528</v>
+        <v>83529</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>137370856</v>
       </c>
       <c r="B108" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>137370860</v>
       </c>
       <c r="B109" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>137370861</v>
       </c>
       <c r="B110" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>137370862</v>
       </c>
       <c r="B111" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>137370864</v>
       </c>
       <c r="B114" t="n">
-        <v>83521</v>
+        <v>83522</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>137370868</v>
       </c>
       <c r="B139" t="n">
-        <v>78537</v>
+        <v>78538</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370850</v>
       </c>
       <c r="B2" t="n">
-        <v>78549</v>
+        <v>78551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137370859</v>
       </c>
       <c r="B29" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137370865</v>
       </c>
       <c r="B30" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137370854</v>
       </c>
       <c r="B31" t="n">
-        <v>83529</v>
+        <v>83531</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>137370856</v>
       </c>
       <c r="B108" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>137370860</v>
       </c>
       <c r="B109" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>137370861</v>
       </c>
       <c r="B110" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>137370862</v>
       </c>
       <c r="B111" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>137370864</v>
       </c>
       <c r="B114" t="n">
-        <v>83522</v>
+        <v>83524</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>137370868</v>
       </c>
       <c r="B139" t="n">
-        <v>78538</v>
+        <v>78540</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>

--- a/artfynd/A 27557-2025 artfynd.xlsx
+++ b/artfynd/A 27557-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370850</v>
       </c>
       <c r="B2" t="n">
-        <v>78551</v>
+        <v>78555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>137370858</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>137370863</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>137370853</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>137370867</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>137370849</v>
       </c>
       <c r="B18" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137370855</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137370866</v>
       </c>
       <c r="B28" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>137370859</v>
       </c>
       <c r="B29" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>137370865</v>
       </c>
       <c r="B30" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>137370854</v>
       </c>
       <c r="B31" t="n">
-        <v>83531</v>
+        <v>83535</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>137370846</v>
       </c>
       <c r="B59" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>137370856</v>
       </c>
       <c r="B108" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>137370860</v>
       </c>
       <c r="B109" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>137370861</v>
       </c>
       <c r="B110" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>137370862</v>
       </c>
       <c r="B111" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>137370864</v>
       </c>
       <c r="B114" t="n">
-        <v>83524</v>
+        <v>83528</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>137370851</v>
       </c>
       <c r="B137" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>137370868</v>
       </c>
       <c r="B139" t="n">
-        <v>78540</v>
+        <v>78544</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
